--- a/outputs/Block2_Second_Exam_Improvement_v12.xlsx
+++ b/outputs/Block2_Second_Exam_Improvement_v12.xlsx
@@ -564,7 +564,7 @@
         <v>8.020000000000001</v>
       </c>
       <c r="C5">
-        <v>5.273583577922919</v>
+        <v>5.27358357792292</v>
       </c>
       <c r="D5">
         <v>3.26807385466284</v>
@@ -576,7 +576,7 @@
         <v>5.760715154417663</v>
       </c>
       <c r="G5">
-        <v>3.01429873234058</v>
+        <v>3.014298732340581</v>
       </c>
       <c r="H5">
         <v>71.82936601518281</v>

--- a/outputs/Block2_Second_Exam_Improvement_v12.xlsx
+++ b/outputs/Block2_Second_Exam_Improvement_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Outcome</t>
   </si>
@@ -46,25 +46,7 @@
     <t>Second Exam Verdict</t>
   </si>
   <si>
-    <t>Democratic House Seats</t>
-  </si>
-  <si>
-    <t>Democratic Senate Seats (national prior)</t>
-  </si>
-  <si>
-    <t>House Seat Margin (D-R)</t>
-  </si>
-  <si>
     <t>Popular Vote Margin (pp)</t>
-  </si>
-  <si>
-    <t>Republican House Seats</t>
-  </si>
-  <si>
-    <t>Republican Senate Seats (national prior)</t>
-  </si>
-  <si>
-    <t>Senate Seat Margin (D-R)</t>
   </si>
   <si>
     <t>Refinement improved outer-test MAE</t>
@@ -425,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -465,223 +447,31 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>36</v>
+        <v>8.020000000000001</v>
       </c>
       <c r="C2">
-        <v>24.4</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="D2">
-        <v>18.6</v>
+        <v>4.47076568678119</v>
       </c>
       <c r="E2">
-        <v>18.6</v>
+        <v>2.259284845582338</v>
       </c>
       <c r="F2">
-        <v>17.4</v>
+        <v>5.760715154417663</v>
       </c>
       <c r="G2">
-        <v>5.799999999999997</v>
+        <v>2.668079547044425</v>
       </c>
       <c r="H2">
-        <v>48.33333333333333</v>
+        <v>71.82936601518281</v>
       </c>
       <c r="I2">
-        <v>23.77049180327868</v>
+        <v>54.14820854404234</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
         <v>11</v>
-      </c>
-      <c r="B3">
-        <v>5.8</v>
-      </c>
-      <c r="C3">
-        <v>4.6</v>
-      </c>
-      <c r="D3">
-        <v>2.8</v>
-      </c>
-      <c r="E3">
-        <v>2.8</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1.8</v>
-      </c>
-      <c r="H3">
-        <v>51.72413793103448</v>
-      </c>
-      <c r="I3">
-        <v>39.1304347826087</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
-        <v>72</v>
-      </c>
-      <c r="C4">
-        <v>48.8</v>
-      </c>
-      <c r="D4">
-        <v>37.2</v>
-      </c>
-      <c r="E4">
-        <v>37.2</v>
-      </c>
-      <c r="F4">
-        <v>34.8</v>
-      </c>
-      <c r="G4">
-        <v>11.59999999999999</v>
-      </c>
-      <c r="H4">
-        <v>48.33333333333333</v>
-      </c>
-      <c r="I4">
-        <v>23.77049180327868</v>
-      </c>
-      <c r="J4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>8.020000000000001</v>
-      </c>
-      <c r="C5">
-        <v>5.27358357792292</v>
-      </c>
-      <c r="D5">
-        <v>3.26807385466284</v>
-      </c>
-      <c r="E5">
-        <v>2.259284845582338</v>
-      </c>
-      <c r="F5">
-        <v>5.760715154417663</v>
-      </c>
-      <c r="G5">
-        <v>3.014298732340581</v>
-      </c>
-      <c r="H5">
-        <v>71.82936601518281</v>
-      </c>
-      <c r="I5">
-        <v>57.158451891414</v>
-      </c>
-      <c r="J5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>36</v>
-      </c>
-      <c r="C6">
-        <v>24.4</v>
-      </c>
-      <c r="D6">
-        <v>18.6</v>
-      </c>
-      <c r="E6">
-        <v>18.6</v>
-      </c>
-      <c r="F6">
-        <v>17.4</v>
-      </c>
-      <c r="G6">
-        <v>5.799999999999997</v>
-      </c>
-      <c r="H6">
-        <v>48.33333333333333</v>
-      </c>
-      <c r="I6">
-        <v>23.77049180327868</v>
-      </c>
-      <c r="J6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>5.6</v>
-      </c>
-      <c r="C7">
-        <v>4.4</v>
-      </c>
-      <c r="D7">
-        <v>2.6</v>
-      </c>
-      <c r="E7">
-        <v>2.6</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1.8</v>
-      </c>
-      <c r="H7">
-        <v>53.57142857142857</v>
-      </c>
-      <c r="I7">
-        <v>40.90909090909091</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>11.4</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>5.4</v>
-      </c>
-      <c r="E8">
-        <v>5.4</v>
-      </c>
-      <c r="F8">
-        <v>6</v>
-      </c>
-      <c r="G8">
-        <v>3.6</v>
-      </c>
-      <c r="H8">
-        <v>52.63157894736842</v>
-      </c>
-      <c r="I8">
-        <v>40</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Second_Exam_Improvement_v12.xlsx
+++ b/outputs/Block2_Second_Exam_Improvement_v12.xlsx
@@ -450,7 +450,7 @@
         <v>8.020000000000001</v>
       </c>
       <c r="C2">
-        <v>4.927364392626764</v>
+        <v>4.927364392626762</v>
       </c>
       <c r="D2">
         <v>4.47076568678119</v>
@@ -462,13 +462,13 @@
         <v>5.760715154417663</v>
       </c>
       <c r="G2">
-        <v>2.668079547044425</v>
+        <v>2.668079547044424</v>
       </c>
       <c r="H2">
         <v>71.82936601518281</v>
       </c>
       <c r="I2">
-        <v>54.14820854404234</v>
+        <v>54.14820854404233</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>

--- a/outputs/Block2_Second_Exam_Improvement_v12.xlsx
+++ b/outputs/Block2_Second_Exam_Improvement_v12.xlsx
@@ -450,7 +450,7 @@
         <v>8.020000000000001</v>
       </c>
       <c r="C2">
-        <v>4.927364392626762</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="D2">
         <v>4.47076568678119</v>
@@ -462,13 +462,13 @@
         <v>5.760715154417663</v>
       </c>
       <c r="G2">
-        <v>2.668079547044424</v>
+        <v>2.668079547044425</v>
       </c>
       <c r="H2">
         <v>71.82936601518281</v>
       </c>
       <c r="I2">
-        <v>54.14820854404233</v>
+        <v>54.14820854404234</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>

--- a/outputs/Block2_Second_Exam_Improvement_v12.xlsx
+++ b/outputs/Block2_Second_Exam_Improvement_v12.xlsx
@@ -450,7 +450,7 @@
         <v>8.020000000000001</v>
       </c>
       <c r="C2">
-        <v>4.927364392626764</v>
+        <v>4.927364392626763</v>
       </c>
       <c r="D2">
         <v>4.47076568678119</v>
@@ -468,7 +468,7 @@
         <v>71.82936601518281</v>
       </c>
       <c r="I2">
-        <v>54.14820854404234</v>
+        <v>54.14820854404233</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>

--- a/outputs/Block2_Second_Exam_Improvement_v12.xlsx
+++ b/outputs/Block2_Second_Exam_Improvement_v12.xlsx
@@ -450,7 +450,7 @@
         <v>8.020000000000001</v>
       </c>
       <c r="C2">
-        <v>4.927364392626763</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="D2">
         <v>4.47076568678119</v>
@@ -468,7 +468,7 @@
         <v>71.82936601518281</v>
       </c>
       <c r="I2">
-        <v>54.14820854404233</v>
+        <v>54.14820854404234</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>

--- a/outputs/Block2_Second_Exam_Improvement_v12.xlsx
+++ b/outputs/Block2_Second_Exam_Improvement_v12.xlsx
@@ -450,7 +450,7 @@
         <v>8.020000000000001</v>
       </c>
       <c r="C2">
-        <v>4.927364392626763</v>
+        <v>4.92736439262676</v>
       </c>
       <c r="D2">
         <v>4.47076568678119</v>
@@ -462,13 +462,13 @@
         <v>5.760715154417663</v>
       </c>
       <c r="G2">
-        <v>2.668079547044425</v>
+        <v>2.668079547044422</v>
       </c>
       <c r="H2">
         <v>71.82936601518281</v>
       </c>
       <c r="I2">
-        <v>54.14820854404233</v>
+        <v>54.14820854404231</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>

--- a/outputs/Block2_Second_Exam_Improvement_v12.xlsx
+++ b/outputs/Block2_Second_Exam_Improvement_v12.xlsx
@@ -450,7 +450,7 @@
         <v>8.020000000000001</v>
       </c>
       <c r="C2">
-        <v>4.92736439262676</v>
+        <v>4.927364392626761</v>
       </c>
       <c r="D2">
         <v>4.47076568678119</v>
@@ -462,13 +462,13 @@
         <v>5.760715154417663</v>
       </c>
       <c r="G2">
-        <v>2.668079547044422</v>
+        <v>2.668079547044423</v>
       </c>
       <c r="H2">
         <v>71.82936601518281</v>
       </c>
       <c r="I2">
-        <v>54.14820854404231</v>
+        <v>54.14820854404232</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>

--- a/outputs/Block2_Second_Exam_Improvement_v12.xlsx
+++ b/outputs/Block2_Second_Exam_Improvement_v12.xlsx
@@ -450,7 +450,7 @@
         <v>8.020000000000001</v>
       </c>
       <c r="C2">
-        <v>4.927364392626761</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="D2">
         <v>4.47076568678119</v>
@@ -462,13 +462,13 @@
         <v>5.760715154417663</v>
       </c>
       <c r="G2">
-        <v>2.668079547044423</v>
+        <v>2.668079547044425</v>
       </c>
       <c r="H2">
         <v>71.82936601518281</v>
       </c>
       <c r="I2">
-        <v>54.14820854404232</v>
+        <v>54.14820854404234</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>
